--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-media-pathology.xlsx
@@ -373,7 +373,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -505,7 +505,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|CarePlan)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1|CarePlan|4.0.1)
 </t>
   </si>
   <si>
@@ -605,7 +605,7 @@
     <t>高水準メディアカテゴリのコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-type</t>
+    <t>http://hl7.org/fhir/ValueSet/media-type|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -659,7 +659,7 @@
     <t>画像を収集する際に使用される投影イメージングビュー。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-view</t>
+    <t>http://hl7.org/fhir/ValueSet/media-view|4.0.1</t>
   </si>
   <si>
     <t>DiagnosticImage.subjectOrientationCode</t>
@@ -804,7 +804,7 @@
     <t>メディアの理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -831,7 +831,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -868,7 +868,7 @@
     <t>Media.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric|Device)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
